--- a/data/trans_camb/IQ2605_R2-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IQ2605_R2-Estudios-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>21,5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>30,22</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>31,96</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>22,77</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>29,79</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>28,43</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>21,5</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>30,22</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,84</t>
+          <t>22,19</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>28,26</t>
+          <t>28,31</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,89; 33,58</t>
+          <t>9,17; 32,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>16,56; 41,55</t>
+          <t>17,67; 40,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,73; 49,22</t>
+          <t>10,28; 45,74</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,31; 34,38</t>
+          <t>10,64; 32,5</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>16,65; 41,57</t>
+          <t>17,56; 41,29</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,73; 43,47</t>
+          <t>-7,04; 42,32</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,93; 30,35</t>
+          <t>13,96; 30,48</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>22,24; 38,5</t>
+          <t>21,28; 38,98</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11,66; 41,73</t>
+          <t>11,79; 40,91</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>41,35%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>58,14%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>61,48%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>45,92%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>60,08%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>57,34%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>41,35%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>58,14%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>53,54%</t>
+          <t>44,74%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>55,68%</t>
+          <t>55,78%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,9; 76,86</t>
+          <t>15,69; 72,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>29,46; 97,81</t>
+          <t>29,54; 90,04</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 110,19</t>
+          <t>19,68; 98,95</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15,08; 78,87</t>
+          <t>19,19; 74,42</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>30,4; 95,22</t>
+          <t>32,8; 97,04</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,53; 93,76</t>
+          <t>-13,98; 91,15</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,76; 67,6</t>
+          <t>25,39; 67,24</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>39,9; 84,05</t>
+          <t>38,6; 85,35</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>22,3; 86,92</t>
+          <t>22,37; 86,96</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>22,85</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>27,14</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>25,5</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>19,06</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>21,27</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>15,42</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>22,85</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>27,14</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>26,01</t>
+          <t>15,01</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>21,57</t>
+          <t>20,98</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13,91; 24,11</t>
+          <t>18,26; 27,72</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16,43; 26,36</t>
+          <t>22,25; 31,79</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,31; 24,68</t>
+          <t>17,61; 33,05</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18,42; 27,93</t>
+          <t>13,56; 24,45</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>22,26; 31,57</t>
+          <t>15,82; 26,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,74; 32,91</t>
+          <t>5,64; 24,03</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,52; 24,71</t>
+          <t>17,2; 24,6</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>20,92; 27,74</t>
+          <t>20,5; 27,72</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>15,57; 27,42</t>
+          <t>15,05; 26,85</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>44,81%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>53,21%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>49,99%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>35,16%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>39,23%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>28,44%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>44,81%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>53,21%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>41,09%</t>
+          <t>39,96%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>24,33; 47,39</t>
+          <t>34,18; 57,74</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>28,46; 51,8</t>
+          <t>41,53; 66,34</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,2; 47,31</t>
+          <t>33,15; 67,33</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>34,16; 57,81</t>
+          <t>23,8; 48,08</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>41,0; 65,47</t>
+          <t>27,64; 51,64</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,29; 66,82</t>
+          <t>9,68; 45,57</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,24; 49,63</t>
+          <t>31,5; 48,79</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>38,26; 54,88</t>
+          <t>37,47; 55,09</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>29,07; 53,35</t>
+          <t>27,52; 52,37</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>12,48</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>22,08</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>15,0</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>19,62</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>20,71</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>19,4</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>12,48</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>22,08</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,68</t>
+          <t>19,57</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>17,1</t>
+          <t>17,37</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>10,22; 27,57</t>
+          <t>4,34; 21,78</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11,92; 28,66</t>
+          <t>14,78; 29,76</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,87; 30,25</t>
+          <t>-2,02; 27,79</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,18; 21,31</t>
+          <t>10,92; 27,9</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,08; 29,84</t>
+          <t>12,34; 28,52</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 27,51</t>
+          <t>7,06; 32,12</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,23; 21,55</t>
+          <t>10,1; 22,07</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>15,67; 26,79</t>
+          <t>15,91; 26,99</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,13; 25,43</t>
+          <t>7,58; 26,13</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>21,26%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>37,62%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>25,55%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>35,28%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>37,25%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>34,88%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>21,26%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>37,62%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>35,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>30,42%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>17,49; 53,46</t>
+          <t>7,05; 41,18</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>19,9; 56,77</t>
+          <t>23,11; 55,64</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10,79; 59,31</t>
+          <t>-3,43; 50,81</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6,71; 40,56</t>
+          <t>18,42; 55,83</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>22,09; 56,11</t>
+          <t>20,79; 57,84</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,26; 49,3</t>
+          <t>12,06; 61,53</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>16,66; 40,02</t>
+          <t>16,97; 41,51</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>25,23; 50,14</t>
+          <t>26,67; 51,13</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>12,19; 46,38</t>
+          <t>13,04; 47,6</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>20,41</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>26,38</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>23,55</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>19,66</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>22,07</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>17,97</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>20,41</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>26,38</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,57</t>
+          <t>17,28</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>21,11</t>
+          <t>20,75</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>15,42; 23,83</t>
+          <t>15,87; 24,04</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>18,16; 26,21</t>
+          <t>22,47; 30,48</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11,12; 24,55</t>
+          <t>17,13; 29,58</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16,57; 24,5</t>
+          <t>14,95; 23,58</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>22,25; 29,85</t>
+          <t>17,88; 25,94</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,62; 29,82</t>
+          <t>10,04; 24,29</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,27; 22,86</t>
+          <t>17,03; 22,87</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>21,53; 27,17</t>
+          <t>21,35; 26,97</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>16,58; 25,74</t>
+          <t>15,56; 25,32</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>38,67%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>49,97%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>44,6%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>36,43%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>40,9%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>33,3%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>38,67%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>49,97%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>44,65%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>39,57%</t>
+          <t>38,88%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>27,33; 46,42</t>
+          <t>28,48; 47,17</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>31,96; 51,59</t>
+          <t>40,9; 60,36</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>20,07; 46,64</t>
+          <t>31,68; 57,74</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>30,16; 48,41</t>
+          <t>26,63; 46,15</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>40,07; 58,91</t>
+          <t>31,9; 50,8</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>31,0; 58,46</t>
+          <t>18,31; 46,55</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,19; 44,15</t>
+          <t>31,03; 44,56</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>39,0; 52,61</t>
+          <t>38,65; 52,23</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>30,85; 49,43</t>
+          <t>28,58; 48,62</t>
         </is>
       </c>
     </row>
